--- a/Docs/TemplateFile/Pipe-Spec.xlsx
+++ b/Docs/TemplateFile/Pipe-Spec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CodeProject\PMC\PMCSystem_Backend\Docs\TemplateFile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BD2DA9-A557-4123-8F6F-A41E50F7A126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57BE956-13C1-4B71-9B80-F0CEB92B1F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Piping Specification</t>
   </si>
@@ -110,14 +110,6 @@
   </si>
   <si>
     <t>NPS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{Standard:Red}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{Standard:Tee}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -178,10 +170,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{{Elbow}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{{standard_Bend}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -207,6 +195,22 @@
   </si>
   <si>
     <t>{{pipingStandard}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{standard_Elbow}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{standard_Red}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{standard_Tee}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{npd_1}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -645,10 +649,10 @@
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -738,10 +742,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -749,7 +753,7 @@
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -757,7 +761,7 @@
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
       <c r="O4" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
@@ -772,7 +776,9 @@
         <v>29</v>
       </c>
       <c r="B5" s="11"/>
-      <c r="C5" s="1"/>
+      <c r="C5" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -851,7 +857,7 @@
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -879,7 +885,7 @@
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D9" s="10"/>
       <c r="E9" s="10"/>
@@ -907,7 +913,7 @@
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D10" s="10"/>
       <c r="E10" s="10"/>
@@ -935,7 +941,7 @@
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -963,7 +969,7 @@
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="7" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10"/>
@@ -991,7 +997,7 @@
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -1019,7 +1025,7 @@
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
@@ -1047,7 +1053,7 @@
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
@@ -1075,7 +1081,7 @@
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
@@ -1103,7 +1109,7 @@
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -1131,7 +1137,7 @@
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
@@ -1159,7 +1165,7 @@
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
@@ -1187,7 +1193,7 @@
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -1215,7 +1221,7 @@
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -1243,7 +1249,7 @@
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -1271,7 +1277,7 @@
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
@@ -1299,7 +1305,7 @@
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
@@ -1327,7 +1333,7 @@
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
